--- a/data/so-good-apartments/project/sponsor_financials.xlsx
+++ b/data/so-good-apartments/project/sponsor_financials.xlsx
@@ -7,17 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sponsor Financials" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sponsor Financials'!$A$1:$H$51</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +30,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,19 +92,70 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,163 +522,1536 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Sponsor Financials – So-Good Apartments JV LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Guarantor Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mike Hoque</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Individual</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Report Date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Audited</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$85000000</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RE Holdings + Cash</t>
-        </is>
-      </c>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>General Information</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>So-Good Apartments</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$35000000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mortgages</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>General Information</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Springfield</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Net Worth</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$50000000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Required &gt; Loan Amt</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>General Information</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unit Count</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Multi-family development</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Liquid Assets</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$4500000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>$2.5M required (10% Loan)</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>General Information</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Total Project Cost</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Includes all hard/soft costs</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>financing</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>and sponsor development fee</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Contingent Liabilities</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$12000000</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Guarantees on other loans</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Development Start Date</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Groundbreaking / Initial Capital Call</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Portfolio DSCR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.35x</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Across all holdings</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Construction Completion Date</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Expected Certificate of Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Lease-Up Commencement Date</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>First units ready for occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Stabilization Date</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Target 90%+ occupancy and market rents</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>approx. 12 months post-completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Project Overview</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Projected Exit Date</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Assumed sale 3 years post-stabilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Capital Structure</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Sources of Funds</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Total Equity Required</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>22750000</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>35% of Total Project Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Capital Structure</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Sources of Funds</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Total Debt Required</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>42250000</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>65% of Total Project Cost (Construction Loan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Capital Structure</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Equity Breakdown</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor (GP) Direct Equity</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>3412500</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>15% of Total Equity Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Capital Structure</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Equity Breakdown</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Limited Partner (LP) Equity</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>19337500</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>85% of Total Equity Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Capital Structure</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Key Ratios</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Loan-to-Cost (LTC)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Construction Loan, based on $65M TCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Capital Structure</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Key Ratios</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Equity-to-Cost (ETC)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Total Equity, based on $65M TCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Development Fees</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Total Development Fee</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>6.15% of Total Project Cost</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>paid over construction period</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Development Fees</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Development Fee - Initial Payment</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Paid at project closing / first draw</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Development Fees</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Development Fee - Mid-Construction Payment</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Paid at 50% construction completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Development Fees</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Development Fee - Completion Payment</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Paid at construction completion / Certificate of Occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Asset Management Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Annual Asset Management Fee (Post-Stabilization)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>160000</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>0.25% of Year 1 Stabilized Value ($64M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Construction Management Fees</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Total Construction Management Fee</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>2.0% of Hard Costs ($40M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Fees</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Leasing Fees</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Lease-Up Brokerage Fee (Internal)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>3.0% of Year 1 Gross Potential Rent ($5.5M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>GP Promote</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Promote - Equity Stake</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>After LP preferred return (e.g.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>8% waterfall)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Key Metrics</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Projected GP Equity Multiple</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Targeted gross return on sponsor equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Key Metrics</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Projected GP Internal Rate of Return (IRR)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Targeted IRR on sponsor equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Key Metrics</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Projected LP Equity Multiple</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Targeted gross return on LP equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Key Metrics</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Projected LP Internal Rate of Return (IRR)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Targeted IRR on LP equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Key Metrics</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Projected Overall Project Equity Multiple</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Blended equity multiple for all equity investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Profitability (Projections)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Key Metrics</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Projected Overall Project IRR</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Blended IRR for all equity investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Sponsor Guarantees</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Loan Guarantees</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Completion Guarantee</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>42250000</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Full construction loan amount until substantial completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Guarantees</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Loan Guarantees</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Recourse Carve-Out Liability Cap</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Standard non-recourse carve-out cap for bad acts</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Guarantees</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Environmental Indemnity</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Standard practice for environmental liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Capital Call</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Q1 2024 (Initial GP Equity)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Initial cash contribution for land acquisition and closing costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Capital Call</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Q2 2024 (GP Equity)</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Second capital call for initial construction draws</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Capital Call</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Q4 2024 (GP Equity)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Third capital call during peak construction phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Capital Call</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Q2 2025 (GP Equity)</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>712500</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Final GP equity capital call to fund project</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Q1 2027 (Deferred Development Fee)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Portion of development fee deferred until stabilization cash flow allows</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Q4 2027 (Refinance/Operating Cash Flow)</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Potential refinance event or operating cash flow distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Q4 2029 (Sale Proceeds - Base Equity)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>3412500</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Return of initial sponsor equity (at project exit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor Capital Flows (Illustrative)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Q4 2029 (Sale Proceeds - Promote)</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Sponsor promote/profit distribution at project exit (estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Operational Projections</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Gross Potential Rent (GPR)</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Annualized GPR at stabilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Operational Projections</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Vacancy &amp; Credit Loss</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Industry standard for multi-family property</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Operational Projections</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Operating Expenses (OpEx)</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>~30% of GPR after vacancy</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>excluding property taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Operational Projections</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Net Operating Income (NOI)</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>3675000</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>GPR less vacancy and OpEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Valuation Metrics</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Exit Cap Rate</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Projected cap rate for disposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Valuation Metrics</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Projected Exit Value</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>63913043</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Based on Stabilized NOI / Exit Cap Rate ($3.675M / 0.0575)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Debt Service</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Annual Debt Service (Stabilized)</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Estimated P&amp;I on permanent financing (e.g. 6.5% on $42.5M</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>30-yr amort)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Key Project Financials (Contextual)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Debt Service</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized Debt Service Coverage Ratio (DSCR)</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Stabilized NOI / Annual Debt Service ($3.675M / $3.2M)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H51"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>